--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M229"/>
+  <dimension ref="A1:M230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3858.08</v>
+        <v>3825.41</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>913.76</v>
+        <v>909.0599999999999</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>609.17</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>609.17</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>609.17</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>718.8200000000001</v>
+        <v>711.65</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>355.35</v>
+        <v>351.8</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>16752.21</v>
+        <v>16585.02</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>584.8</v>
+        <v>578.97</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>304.59</v>
+        <v>301.55</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>39507.8</v>
+        <v>39113.51</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>76199.84</v>
+        <v>75439.36</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>710.7</v>
+        <v>703.61</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>20305.71</v>
+        <v>20093.06</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>82301.88</v>
+        <v>81852.03</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>137.32</v>
+        <v>135.79</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>145.69</v>
+        <v>144.07</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>355.35</v>
+        <v>351.39</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27595.46</v>
+        <v>27288</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15828.3</v>
+        <v>15651.95</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>253.82</v>
+        <v>250.99</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>4213.33</v>
+        <v>4190.25</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>28510.75</v>
+        <v>28474.46</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1615.91</v>
+        <v>1621.67</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>14293.19</v>
+        <v>14344.2</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>324.89</v>
+        <v>326.05</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>25220.7</v>
+        <v>25310.71</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6350.61</v>
+        <v>6373.28</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>19405.66</v>
+        <v>19474.91</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>220.32</v>
+        <v>222.71</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>355.35</v>
+        <v>359.22</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>304.59</v>
+        <v>307.9</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>162.45</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>152.29</v>
+        <v>153.95</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>314.74</v>
+        <v>318.16</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>659.9299999999999</v>
+        <v>667.11</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>101.53</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>304.59</v>
+        <v>305.59</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>507.64</v>
+        <v>509.31</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>50.76</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>304.59</v>
+        <v>305.59</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>101.53</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>19286.07</v>
+        <v>19618.97</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>20305.71</v>
+        <v>20656.22</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>15186.53</v>
+        <v>15448.68</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>253.82</v>
+        <v>258.2</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>13371.31</v>
+        <v>13433.58</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>13490.26</v>
+        <v>13587.51</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>28410.08</v>
+        <v>28614.9</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1833.93</v>
+        <v>1847.15</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>9676.200000000001</v>
+        <v>9745.959999999999</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>21070.98</v>
+        <v>21222.88</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>609.17</v>
+        <v>606.66</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>25788.25</v>
+        <v>25681.96</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>261.75</v>
+        <v>261.35</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2013.47</v>
+        <v>2023.87</v>
       </c>
     </row>
     <row r="58">
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5033.68</v>
+        <v>5059.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4337-696-CM25</t>
+          <t>2085-1058-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>805.39</v>
+        <v>1020.53</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2085-1058-CM25</t>
+          <t>4337-696-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1015.29</v>
+        <v>809.55</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>752.38</v>
+        <v>756.27</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>25476.97</v>
+        <v>25656.77</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>518.47</v>
+        <v>511.77</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8994.93</v>
+        <v>8880.68</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>87320.71000000001</v>
+        <v>86451.91</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>37307.77</v>
+        <v>36936.58</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>46890.13</v>
+        <v>46721.99</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>16372.63</v>
+        <v>16313.92</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>17627.87</v>
+        <v>17564.66</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>14392.63</v>
+        <v>14341.03</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2921.87</v>
+        <v>2911.39</v>
       </c>
     </row>
     <row r="72">
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>51.85</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1079659-440-CM25</t>
+          <t>1057389-10579-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4865,17 +4865,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1810.49</v>
+        <v>23894.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057389-10579-CM25</t>
+          <t>1079659-440-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4926,17 +4926,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>23995.41</v>
+        <v>1802.9</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6786.13</v>
+        <v>6707.59</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>31108.52</v>
+        <v>30748.5</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>52886.2</v>
+        <v>52274.14</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2689.48</v>
+        <v>2666.7</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>41.48</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>62.22</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>62.22</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>26405.51</v>
+        <v>26384.28</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>16191.72</v>
+        <v>16178.7</v>
       </c>
     </row>
     <row r="84">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>7743.3</v>
+        <v>7737.08</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1078177-1611-CM25</t>
+          <t>1078177-1610-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5957.18</v>
+        <v>19134.27</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1078177-1610-CM25</t>
+          <t>1078177-1611-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>19047.95</v>
+        <v>5984.18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1078177-1608-CM25</t>
+          <t>1078177-1605-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>24746.42</v>
+        <v>30933.36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1078177-1605-CM25</t>
+          <t>1078177-1608-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>30793.81</v>
+        <v>24858.56</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>14091.41</v>
+        <v>14128.77</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>24240.39</v>
+        <v>24304.67</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>20738.67</v>
+        <v>20793.66</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>12018.06</v>
+        <v>12049.93</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>125.52</v>
+        <v>125.35</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3274.53</v>
+        <v>3269.93</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>51.85</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>13735.55</v>
+        <v>13882.88</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>545.75</v>
+        <v>552.77</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>31542.73</v>
+        <v>30737.26</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>70543.89</v>
+        <v>69532.77</v>
       </c>
     </row>
     <row r="100">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>14648.19</v>
+        <v>14462.26</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>1383-2-CM26</t>
+          <t>2202-17-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6573,17 +6573,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>8825.99</v>
+        <v>15888.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1057387-14-CM26</t>
+          <t>1383-2-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6634,17 +6634,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>26491.41</v>
+        <v>8698.809999999999</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2202-17-CM26</t>
+          <t>1057387-14-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>16120.53</v>
+        <v>26109.67</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>644.8200000000001</v>
+        <v>643.55</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>48490.57</v>
+        <v>48395.07</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>43994.01</v>
+        <v>43907.37</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>13637.97</v>
+        <v>13552.51</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>268.68</v>
+        <v>272.29</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>36990.18</v>
+        <v>37889.7</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>28768.5</v>
+        <v>29495.77</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>662.47</v>
+        <v>682.5599999999999</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>9229.43</v>
+        <v>9509.299999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2204.12</v>
+        <v>2187.63</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>19286.09</v>
+        <v>19385.72</v>
       </c>
     </row>
     <row r="115">
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>80044.55</v>
+        <v>79707.05</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2202-193-CM26</t>
+          <t>1057387-70-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>551.03</v>
+        <v>30749.08</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1950-417-CM26</t>
+          <t>2202-193-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>23201.32</v>
+        <v>552.54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1057387-70-CM26</t>
+          <t>1950-417-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>30664.89</v>
+        <v>23265.02</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>17043.18</v>
+        <v>17198.2</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>19203.44</v>
+        <v>19374.48</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3676.48</v>
+        <v>3670.18</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>25465.36</v>
+        <v>25421.71</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3735.41</v>
+        <v>3731.56</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>16913.36</v>
+        <v>16895.91</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>13968.42</v>
+        <v>13947.87</v>
       </c>
     </row>
     <row r="126">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>17439.97</v>
+        <v>17344.99</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1383-49-CM26</t>
+          <t>2085-172-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8194,13 +8194,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>10257.88</v>
+        <v>1408.02</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2085-172-CM26</t>
+          <t>1383-49-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8220,17 +8220,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1416.37</v>
+        <v>10197.43</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>35857.15</v>
+        <v>35718.75</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>42109.26</v>
+        <v>42327.27</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>18271.37</v>
+        <v>18572.51</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1740.86</v>
+        <v>1745.15</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>6963.45</v>
+        <v>6980.59</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>68942.75</v>
+        <v>69112.38</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>14572</v>
+        <v>14607.85</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>25711.69</v>
+        <v>25530.24</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>26376.72</v>
+        <v>26375.36</v>
       </c>
     </row>
     <row r="138">
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>27010.31</v>
+        <v>27033.58</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1078177-161-CM26</t>
+          <t>1078177-158-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>5530.48</v>
+        <v>21100.98</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1078177-158-CM26</t>
+          <t>1078177-161-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>21014.17</v>
+        <v>5553.33</v>
       </c>
     </row>
     <row r="141">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>12158.71</v>
+        <v>11977.36</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1079659-100-CM26</t>
+          <t>1078177-160-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>50954.69</v>
+        <v>15984.1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1078177-160-CM26</t>
+          <t>1079659-100-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>16087.16</v>
+        <v>50628.25</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3533-88-CM26</t>
+          <t>1079659-102-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>61.101.013-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>988.99</v>
+        <v>4189.98</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1079659-102-CM26</t>
+          <t>1383-88-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9257,17 +9257,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>4251.49</v>
+        <v>8418.030000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1383-88-CM26</t>
+          <t>3533-88-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9318,17 +9318,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.101.013-3</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8541.610000000001</v>
+        <v>974.6900000000001</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>12732.24</v>
+        <v>12458.3</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3587.95</v>
+        <v>3510.75</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>28459.91</v>
+        <v>27797.68</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>17232.79</v>
+        <v>16831.8</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1583.72</v>
+        <v>1533.22</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>264.76</v>
+        <v>259.96</v>
       </c>
     </row>
     <row r="153">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>17220.67</v>
+        <v>16908.37</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1057387-175-CM26</t>
+          <t>1057389-1859-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>29968.36</v>
+        <v>75656.58</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1057389-1859-CM26</t>
+          <t>1057387-175-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>77738.14</v>
+        <v>29165.91</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>22218.85</v>
+        <v>22283.53</v>
       </c>
     </row>
     <row r="157">
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3118.44</v>
+        <v>3144.9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1078177-239-CM26</t>
+          <t>1078177-249-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>24734.87</v>
+        <v>7811.13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1078177-240-CM26</t>
+          <t>1950-947-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10116,12 +10116,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>32706.15</v>
+        <v>46697.43</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1078177-249-CM26</t>
+          <t>1078177-240-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>7824.21</v>
+        <v>32651.46</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1950-947-CM26</t>
+          <t>1078177-239-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>46775.64</v>
+        <v>24693.51</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>18927.29</v>
+        <v>19174.28</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>1372.11</v>
+        <v>1387.72</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>14293.7</v>
+        <v>14456.26</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>1781.96</v>
+        <v>1793.36</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>882.0700000000001</v>
+        <v>887.71</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>54287</v>
+        <v>54512.01</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>9503.32</v>
+        <v>9542.709999999999</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>28482.87</v>
+        <v>28360.52</v>
       </c>
     </row>
     <row r="170">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>16719.12</v>
+        <v>16576.52</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2202-527-CM26</t>
+          <t>1057389-2366-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>23812.5</v>
+        <v>78178.38</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1057389-2366-CM26</t>
+          <t>2202-527-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>77759.64</v>
+        <v>23940.73</v>
       </c>
     </row>
     <row r="173">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>28997.06</v>
+        <v>29216.69</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1078177-352-CM26</t>
+          <t>1950-1039-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11031,12 +11031,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>8280.4</v>
+        <v>46964.58</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1078177-355-CM26</t>
+          <t>1078177-352-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>23973.36</v>
+        <v>8311.77</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1950-1039-CM26</t>
+          <t>1078177-355-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>46787.32</v>
+        <v>24064.19</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>31788.1</v>
+        <v>32024.92</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>18454.16</v>
+        <v>18270.12</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>245.09</v>
+        <v>244.01</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>17079.59</v>
+        <v>17004.73</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2744.98</v>
+        <v>2738.2</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>56234.53</v>
+        <v>56095.67</v>
       </c>
     </row>
     <row r="183">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>334.21</v>
+        <v>335.85</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2085-430-CM26</t>
+          <t>1078177-407-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2222.5</v>
+        <v>295.08</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2085-426-CM26</t>
+          <t>2085-424-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2222.5</v>
+        <v>31942.39</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2085-424-CM26</t>
+          <t>2085-426-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>31836.78</v>
+        <v>2229.87</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1078177-407-CM26</t>
+          <t>2085-430-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11824,12 +11824,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>294.11</v>
+        <v>2229.87</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>9486.110000000001</v>
+        <v>9516.299999999999</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1266.22</v>
+        <v>1281.07</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>14567.62</v>
+        <v>14813.99</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>18928.82</v>
+        <v>19106.36</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>29096.96</v>
+        <v>28605.35</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>977.26</v>
+        <v>960.75</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>77265.00999999999</v>
+        <v>76168.44</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>24522.29</v>
+        <v>24370.26</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>7092</v>
+        <v>7048.03</v>
       </c>
     </row>
     <row r="197">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>18771.08</v>
+        <v>18654.71</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1079659-233-CM26</t>
+          <t>1078177-492-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3104.33</v>
+        <v>31841.32</v>
       </c>
     </row>
     <row r="199">
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>43170.98</v>
+        <v>43367.05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1078177-492-CM26</t>
+          <t>1079659-233-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>31697.36</v>
+        <v>3118.43</v>
       </c>
     </row>
     <row r="201">
@@ -12712,13 +12712,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>110418.12</v>
+        <v>112062.28</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>722-67-CM26</t>
+          <t>2202-687-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12738,17 +12738,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12773,13 +12773,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>423.74</v>
+        <v>321.48</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>722-68-CM26</t>
+          <t>722-67-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12834,13 +12834,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>409.13</v>
+        <v>431.8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2202-687-CM26</t>
+          <t>722-68-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12860,17 +12860,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>315.48</v>
+        <v>416.91</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>14627.14</v>
+        <v>14588.45</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>56179.04</v>
+        <v>55430.72</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>34427.08</v>
+        <v>33753.22</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>9220.91</v>
+        <v>9084.299999999999</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>8421.32</v>
+        <v>8506.02</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>501.07</v>
+        <v>506.09</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>16175.26</v>
+        <v>16337.23</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1326.57</v>
+        <v>1333.33</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>74198.74000000001</v>
+        <v>74487.58</v>
       </c>
     </row>
     <row r="214">
@@ -13505,13 +13505,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>44039.31</v>
+        <v>44210.75</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2202-764-CM26</t>
+          <t>1057387-371-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13536,12 +13536,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -13566,13 +13566,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>20790.14</v>
+        <v>29774</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1057387-371-CM26</t>
+          <t>2202-764-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>29925.6</v>
+        <v>20684.83</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>31872.97</v>
+        <v>31946.06</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>30854.68</v>
+        <v>31061.2</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7247.6</v>
+        <v>7298.32</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>9680.309999999999</v>
+        <v>9748.059999999999</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>55942.86</v>
+        <v>56334.37</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>18302.69</v>
+        <v>18244.88</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>24402.89</v>
+        <v>24325.81</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>15228.28</v>
+        <v>15195.15</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>12632.19</v>
+        <v>12428.34</v>
       </c>
     </row>
     <row r="226">
@@ -14237,13 +14237,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1546.77</v>
+        <v>1521.97</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2085-617-CM26</t>
+          <t>3290-214-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14268,12 +14268,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14283,12 +14283,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14298,13 +14298,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>31649.86</v>
+        <v>17910.93</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3290-214-CM26</t>
+          <t>2085-617-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14329,12 +14329,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14344,12 +14344,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>18010.78</v>
+        <v>31474.4</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,68 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>315.8</v>
+        <v>317.91</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1426099-177-CM26</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="n">
+        <v>2647.93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +27277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +28057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +28122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +28187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +28252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +28317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +29032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +29097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +29162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +29227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +29292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +30007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +30072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +30137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +30202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +30267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +30332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +31047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +31112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +31177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +31242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +31307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +31372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +32022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +32087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +32152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +32217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +32282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +32347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +32477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32607,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +33062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +33127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +33192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +33257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +33322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +33387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33647,11 @@
           <t>76.032.107-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33842,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +34037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +34102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +34167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +34232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +34297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +34362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +34427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +34492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +35012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +35077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +35142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +35207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +35272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +35337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +35402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +35467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35857,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +36052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +36117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +36182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +36247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +36312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +36377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +36442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +36507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +37027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +37153,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +37218,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +37283,11 @@
           <t>96.556.930-8</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
@@ -37092,7 +37092,11 @@
           <t>76.045.081-2</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M567"/>
+  <dimension ref="A1:M592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2724,7 +2724,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2085-196-CM25</t>
+          <t>2103-146-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2783,13 +2783,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2050.69</v>
+        <v>12087.55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2103-146-CM25</t>
+          <t>2085-196-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12087.55</v>
+        <v>2050.69</v>
       </c>
     </row>
     <row r="38">
@@ -3114,7 +3114,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1950-3433-CM25</t>
+          <t>2085-218-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>60128.59</v>
+        <v>2037.84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2085-218-CM25</t>
+          <t>1950-3433-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2037.84</v>
+        <v>60128.59</v>
       </c>
     </row>
     <row r="44">
@@ -3699,7 +3699,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2085-235-CM25</t>
+          <t>1202512-34-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1830.45</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1202512-31-CM25</t>
+          <t>1202512-33-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>8689.459999999999</v>
+        <v>755.6</v>
       </c>
     </row>
     <row r="53">
@@ -3894,7 +3894,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1202512-33-CM25</t>
+          <t>2085-235-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>755.6</v>
+        <v>1830.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1202512-34-CM25</t>
+          <t>1202512-31-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>21.91</v>
+        <v>8689.459999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4349,7 +4349,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>707423-34-CM25</t>
+          <t>2202-322-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11539.66</v>
+        <v>14603.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2202-322-CM25</t>
+          <t>707423-34-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>14603.1</v>
+        <v>11539.66</v>
       </c>
     </row>
     <row r="63">
@@ -4739,7 +4739,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4406-266-CM25</t>
+          <t>3869-290-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.191.200-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,13 +4798,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>17916.86</v>
+        <v>454.21</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3869-290-CM25</t>
+          <t>4406-266-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4829,12 +4829,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.191.200-0</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Municipalidad de Gorbea</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4863,13 +4863,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>454.21</v>
+        <v>17916.86</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2546-346-CM25</t>
+          <t>2546-329-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4928,13 +4928,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>16663.55</v>
+        <v>7298.87</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2546-329-CM25</t>
+          <t>3922-286-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4954,17 +4954,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>7298.87</v>
+        <v>494.2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3922-286-CM25</t>
+          <t>1057388-1251-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>494.2</v>
+        <v>12695.92</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057388-1251-CM25</t>
+          <t>2546-346-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5084,17 +5084,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>12695.92</v>
+        <v>16663.55</v>
       </c>
     </row>
     <row r="73">
@@ -5389,7 +5389,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2085-374-CM25</t>
+          <t>3533-118-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.101.013-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>26142.39</v>
+        <v>736.1799999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3533-118-CM25</t>
+          <t>2085-374-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.101.013-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>736.1799999999999</v>
+        <v>26142.39</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1078177-307-CM25</t>
+          <t>1078177-300-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>34647.94</v>
+        <v>17185.4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4113-281-CM25</t>
+          <t>1078177-309-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>70.766.500-9</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>6399.73</v>
+        <v>57997.18</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1078177-309-CM25</t>
+          <t>4113-281-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>70.766.500-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>57997.18</v>
+        <v>6399.73</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1078177-300-CM25</t>
+          <t>1078177-307-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>17185.4</v>
+        <v>34647.94</v>
       </c>
     </row>
     <row r="83">
@@ -5844,7 +5844,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>722-76-CM25</t>
+          <t>3869-351-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.191.200-0</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>379.28</v>
+        <v>327.77</v>
       </c>
     </row>
     <row r="85">
@@ -5974,7 +5974,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3869-351-CM25</t>
+          <t>722-76-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.191.200-0</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Municipalidad de Gorbea</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>327.77</v>
+        <v>379.28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2202-427-CM25</t>
+          <t>2103-276-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>502.41</v>
+        <v>13596.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2103-276-CM25</t>
+          <t>2202-427-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13596.46</v>
+        <v>502.41</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1057389-3357-CM25</t>
+          <t>2202-425-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,13 +6228,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>73230.92</v>
+        <v>12560.29</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2202-425-CM25</t>
+          <t>1057389-3357-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>12560.29</v>
+        <v>73230.92</v>
       </c>
     </row>
     <row r="91">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3922-355-CM25</t>
+          <t>3922-347-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>504.67</v>
+        <v>383.55</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3922-347-CM25</t>
+          <t>3922-355-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>383.55</v>
+        <v>504.67</v>
       </c>
     </row>
     <row r="95">
@@ -6884,7 +6884,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1338-66-CM25</t>
+          <t>3428-174-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.901.011-8</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1695.8</v>
+        <v>109317.46</v>
       </c>
     </row>
     <row r="101">
@@ -7079,7 +7079,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3428-174-CM25</t>
+          <t>1338-66-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>60.901.011-8</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>109317.46</v>
+        <v>1695.8</v>
       </c>
     </row>
     <row r="104">
@@ -7404,7 +7404,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2085-479-CM25</t>
+          <t>1950-3900-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7424,17 +7424,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7463,13 +7463,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>26020.15</v>
+        <v>55670.7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>1950-3900-CM25</t>
+          <t>2085-479-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7489,17 +7489,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>55670.7</v>
+        <v>26020.15</v>
       </c>
     </row>
     <row r="110">
@@ -7664,7 +7664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2085-488-CM25</t>
+          <t>3922-428-CM25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2017.05</v>
+        <v>1613.64</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1968-1212-CM25</t>
+          <t>3922-429-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>72613.78</v>
+        <v>201.71</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3922-429-CM25</t>
+          <t>1968-1212-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7853,13 +7853,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>201.71</v>
+        <v>72613.78</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3922-428-CM25</t>
+          <t>2085-488-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,7 +7918,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1613.64</v>
+        <v>2017.05</v>
       </c>
     </row>
     <row r="116">
@@ -8184,7 +8184,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3460-166-CM25</t>
+          <t>3922-508-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8204,17 +8204,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.101.069-9</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2134.27</v>
+        <v>354.82</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3922-508-CM25</t>
+          <t>3922-509-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>354.82</v>
+        <v>506.89</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>3922-509-CM25</t>
+          <t>3460-166-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>506.89</v>
+        <v>2134.27</v>
       </c>
     </row>
     <row r="123">
@@ -9094,7 +9094,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1383-266-CM25</t>
+          <t>1968-1529-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -9153,13 +9153,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>3983.99</v>
+        <v>694.23</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1968-1529-CM25</t>
+          <t>1383-266-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>694.23</v>
+        <v>3983.99</v>
       </c>
     </row>
     <row r="136">
@@ -9549,7 +9549,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2202-609-CM25</t>
+          <t>3290-238-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>15155.06</v>
+        <v>5314.17</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>3290-238-CM25</t>
+          <t>2202-609-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>5314.17</v>
+        <v>15155.06</v>
       </c>
     </row>
     <row r="143">
@@ -10199,7 +10199,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1383-299-CM25</t>
+          <t>4513-90-CM25</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10258,13 +10258,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>8632.959999999999</v>
+        <v>13269.42</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>4513-90-CM25</t>
+          <t>1383-299-CM25</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10323,7 +10323,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>13269.42</v>
+        <v>8632.959999999999</v>
       </c>
     </row>
     <row r="153">
@@ -10589,7 +10589,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3290-252-CM25</t>
+          <t>3935-133-CM25</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10648,13 +10648,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>7259.3</v>
+        <v>24589.57</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>3935-133-CM25</t>
+          <t>3460-219-CM25</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10674,17 +10674,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10713,7 +10713,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>24589.57</v>
+        <v>3111.13</v>
       </c>
     </row>
     <row r="159">
@@ -10784,7 +10784,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3460-219-CM25</t>
+          <t>3290-252-CM25</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10804,17 +10804,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.101.069-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10843,13 +10843,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3111.13</v>
+        <v>7259.3</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2202-717-CM25</t>
+          <t>3922-763-CM25</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10908,13 +10908,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>15734.66</v>
+        <v>491.71</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3922-763-CM25</t>
+          <t>3922-756-CM25</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10973,13 +10973,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>491.71</v>
+        <v>983.42</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>3922-756-CM25</t>
+          <t>2202-717-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10999,17 +10999,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>983.42</v>
+        <v>15734.66</v>
       </c>
     </row>
     <row r="164">
@@ -11369,7 +11369,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>707423-110-CM25</t>
+          <t>1078177-935-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11389,17 +11389,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11428,13 +11428,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1531.01</v>
+        <v>1485.54</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1078177-935-CM25</t>
+          <t>707423-110-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11454,17 +11454,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1485.54</v>
+        <v>1531.01</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1078177-946-CM25</t>
+          <t>1968-2030-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>19670.43</v>
+        <v>1260.01</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1968-2030-CM25</t>
+          <t>1078177-944-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1260.01</v>
+        <v>6678.84</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1078177-944-CM25</t>
+          <t>1078177-946-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>6678.84</v>
+        <v>19670.43</v>
       </c>
     </row>
     <row r="174">
@@ -11889,7 +11889,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1383-332-CM25</t>
+          <t>1057388-1485-CM25</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11909,17 +11909,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11948,13 +11948,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>9435.42</v>
+        <v>12945.38</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1057388-1485-CM25</t>
+          <t>1383-332-CM25</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11974,17 +11974,17 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -12013,7 +12013,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>12945.38</v>
+        <v>9435.42</v>
       </c>
     </row>
     <row r="179">
@@ -12344,7 +12344,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1589-94-CM25</t>
+          <t>1079659-310-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12364,17 +12364,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>273.5</v>
+        <v>32477.62</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1079659-310-CM25</t>
+          <t>1589-94-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12429,17 +12429,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>32477.62</v>
+        <v>273.5</v>
       </c>
     </row>
     <row r="186">
@@ -12604,7 +12604,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>707423-137-CM25</t>
+          <t>1028897-1152-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>154.9</v>
+        <v>3098.05</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1028897-1152-CM25</t>
+          <t>707423-137-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3098.05</v>
+        <v>154.9</v>
       </c>
     </row>
     <row r="190">
@@ -13059,7 +13059,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3922-889-CM25</t>
+          <t>3922-890-CM25</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -13118,13 +13118,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>689.42</v>
+        <v>492.44</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>3922-890-CM25</t>
+          <t>3922-889-CM25</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>492.44</v>
+        <v>689.42</v>
       </c>
     </row>
     <row r="197">
@@ -13579,7 +13579,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1078177-1114-CM25</t>
+          <t>1078177-1107-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13638,13 +13638,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>13515.18</v>
+        <v>5028.55</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1078177-1107-CM25</t>
+          <t>1078177-1114-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>5028.55</v>
+        <v>13515.18</v>
       </c>
     </row>
     <row r="205">
@@ -13774,7 +13774,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2085-837-CM25</t>
+          <t>1078177-1131-CM25</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1997.6</v>
+        <v>24493.61</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1078177-1141-CM25</t>
+          <t>2085-837-CM25</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13864,12 +13864,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>12941.97</v>
+        <v>1997.6</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1344300-33-CM25</t>
+          <t>1078177-1141-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>1017.73</v>
+        <v>12941.97</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1344300-34-CM25</t>
+          <t>1344300-33-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>190.59</v>
+        <v>1017.73</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1078177-1131-CM25</t>
+          <t>1344300-34-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>24493.61</v>
+        <v>190.59</v>
       </c>
     </row>
     <row r="211">
@@ -14229,7 +14229,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3922-943-CM25</t>
+          <t>3922-956-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>198.66</v>
+        <v>546.3099999999999</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3922-942-CM25</t>
+          <t>3922-955-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14314,7 +14314,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -14353,13 +14353,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>496.64</v>
+        <v>595.97</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2085-878-CM25</t>
+          <t>3922-943-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>30151.24</v>
+        <v>198.66</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3922-955-CM25</t>
+          <t>3922-944-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14444,7 +14444,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>595.97</v>
+        <v>397.32</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3922-956-CM25</t>
+          <t>2085-878-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14509,17 +14509,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>546.3099999999999</v>
+        <v>30151.24</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3922-944-CM25</t>
+          <t>3922-942-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>397.32</v>
+        <v>496.64</v>
       </c>
     </row>
     <row r="219">
@@ -15139,7 +15139,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1057389-9793-CM25</t>
+          <t>1079659-356-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>71460.82000000001</v>
+        <v>38230.29</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2202-912-CM25</t>
+          <t>2103-598-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>15312.86</v>
+        <v>14374.33</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2103-598-CM25</t>
+          <t>1057389-9793-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15294,12 +15294,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15328,13 +15328,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>14374.33</v>
+        <v>71460.82000000001</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1079659-356-CM25</t>
+          <t>2202-912-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>38230.29</v>
+        <v>15312.86</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2388-325-CM25</t>
+          <t>4112-199-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15419,17 +15419,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1322.61</v>
+        <v>22113.62</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4112-199-CM25</t>
+          <t>1078177-1223-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15489,12 +15489,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15523,13 +15523,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>22113.62</v>
+        <v>5733.75</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1078177-1223-CM25</t>
+          <t>2388-325-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15549,17 +15549,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15588,13 +15588,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>5733.75</v>
+        <v>1322.61</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3922-1040-CM25</t>
+          <t>1057387-657-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15614,17 +15614,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>851.1</v>
+        <v>25468.98</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1057387-657-CM25</t>
+          <t>3922-1040-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.602.223-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>25468.98</v>
+        <v>851.1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1950-4916-CM25</t>
+          <t>3533-334-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15749,12 +15749,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.101.013-3</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,13 +15783,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>41611.98</v>
+        <v>33190.27</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2202-926-CM25</t>
+          <t>1950-4916-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>198.4</v>
+        <v>41611.98</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2388-332-CM25</t>
+          <t>2202-926-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15874,17 +15874,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1378.36</v>
+        <v>198.4</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3533-334-CM25</t>
+          <t>2388-332-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15939,17 +15939,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.101.013-3</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,13 +15978,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>33190.27</v>
+        <v>1378.36</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>4306-498-CM25</t>
+          <t>1075337-14496-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -16004,17 +16004,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.180.600-6</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ERCILLA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -16043,13 +16043,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>17173.57</v>
+        <v>43753.29</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1075337-14496-CM25</t>
+          <t>4306-498-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -16069,17 +16069,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.180.600-6</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE ERCILLA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -16108,7 +16108,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>43753.29</v>
+        <v>17173.57</v>
       </c>
     </row>
     <row r="242">
@@ -16179,7 +16179,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1078177-1263-CM25</t>
+          <t>3922-1069-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16199,17 +16199,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>24051.8</v>
+        <v>420.29</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1078177-1283-CM25</t>
+          <t>1078177-1263-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>18019.23</v>
+        <v>24051.8</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>3922-1069-CM25</t>
+          <t>1078177-1283-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16329,17 +16329,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>420.29</v>
+        <v>18019.23</v>
       </c>
     </row>
     <row r="246">
@@ -16699,7 +16699,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1383-409-CM25</t>
+          <t>3428-345-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16719,17 +16719,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>8026.46</v>
+        <v>85484.03999999999</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3428-345-CM25</t>
+          <t>1383-409-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16784,17 +16784,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16823,13 +16823,13 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>85484.03999999999</v>
+        <v>8026.46</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1075337-14611-CM25</t>
+          <t>3428-352-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -16888,13 +16888,13 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>31676.19</v>
+        <v>873.21</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3922-1144-CM25</t>
+          <t>1078177-1305-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16914,17 +16914,17 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>202.52</v>
+        <v>13663.86</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>3922-1145-CM25</t>
+          <t>1075337-14611-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>101.26</v>
+        <v>31676.19</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3922-1146-CM25</t>
+          <t>3922-1144-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17044,7 +17044,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -17089,7 +17089,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>3922-1147-CM25</t>
+          <t>3922-1146-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>212.64</v>
+        <v>202.52</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3922-1148-CM25</t>
+          <t>3922-1145-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>222.77</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3922-1149-CM25</t>
+          <t>3922-1148-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>506.29</v>
+        <v>222.77</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>3922-1151-CM25</t>
+          <t>3922-1149-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>810.0700000000001</v>
+        <v>506.29</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1383-422-CM25</t>
+          <t>3922-1151-CM25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17369,17 +17369,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,13 +17408,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>135.56</v>
+        <v>810.0700000000001</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1078177-1305-CM25</t>
+          <t>1383-422-CM25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17434,17 +17434,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>13663.86</v>
+        <v>135.56</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>3428-352-CM25</t>
+          <t>3922-1147-CM25</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17538,7 +17538,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>873.21</v>
+        <v>212.64</v>
       </c>
     </row>
     <row r="264">
@@ -17869,7 +17869,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>3922-1225-CM25</t>
+          <t>2202-986-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17894,12 +17894,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17928,13 +17928,13 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>301.55</v>
+        <v>16585.02</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>3460-329-CM25</t>
+          <t>3922-1232-CM25</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.101.069-9</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,13 +17993,13 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>75439.36</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1950-13576-CM25</t>
+          <t>3922-1231-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18024,12 +18024,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18058,13 +18058,13 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>39113.51</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3922-1226-CM25</t>
+          <t>3922-1230-CM25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18123,13 +18123,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>578.97</v>
+        <v>603.09</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3922-1227-CM25</t>
+          <t>3922-1225-CM25</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18188,7 +18188,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>703.61</v>
+        <v>301.55</v>
       </c>
     </row>
     <row r="274">
@@ -18259,7 +18259,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3922-1229-CM25</t>
+          <t>3922-1227-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>711.65</v>
+        <v>703.61</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>3922-1230-CM25</t>
+          <t>3922-1226-CM25</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>603.09</v>
+        <v>578.97</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3922-1231-CM25</t>
+          <t>1950-13576-CM25</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18448,13 +18448,13 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>603.09</v>
+        <v>39113.51</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3922-1232-CM25</t>
+          <t>3922-1229-CM25</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18513,13 +18513,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>603.09</v>
+        <v>711.65</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2202-986-CM25</t>
+          <t>3460-329-CM25</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18578,7 +18578,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>16585.02</v>
+        <v>75439.36</v>
       </c>
     </row>
     <row r="280">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2103-676-CM25</t>
+          <t>3922-1249-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18864,17 +18864,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,7 +18903,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>15651.95</v>
+        <v>144.07</v>
       </c>
     </row>
     <row r="285">
@@ -18974,7 +18974,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>3922-1249-CM25</t>
+          <t>3922-1247-CM25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>144.07</v>
+        <v>250.99</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>3922-1248-CM25</t>
+          <t>2103-676-CM25</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19059,17 +19059,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>351.39</v>
+        <v>15651.95</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>3922-1247-CM25</t>
+          <t>3922-1248-CM25</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19163,7 +19163,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>250.99</v>
+        <v>351.39</v>
       </c>
     </row>
     <row r="289">
@@ -19299,7 +19299,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>3922-1282-CM25</t>
+          <t>1078177-1420-CM25</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19319,17 +19319,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>326.05</v>
+        <v>6373.28</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>707423-196-CM25</t>
+          <t>1078177-1423-CM25</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>1621.67</v>
+        <v>25310.71</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1078177-1444-CM25</t>
+          <t>1078177-1429-CM25</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19488,13 +19488,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>14344.2</v>
+        <v>19474.91</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1078177-1429-CM25</t>
+          <t>1078177-1444-CM25</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19553,13 +19553,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>19474.91</v>
+        <v>14344.2</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1078177-1423-CM25</t>
+          <t>707423-196-CM25</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19584,12 +19584,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>25310.71</v>
+        <v>1621.67</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1078177-1420-CM25</t>
+          <t>3922-1282-CM25</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19644,17 +19644,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19683,13 +19683,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>6373.28</v>
+        <v>326.05</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3922-1284-CM25</t>
+          <t>3922-1290-CM25</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -19748,13 +19748,13 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>222.71</v>
+        <v>667.11</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>3922-1286-CM25</t>
+          <t>3922-1288-CM25</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19813,13 +19813,13 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>307.9</v>
+        <v>153.95</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3922-1285-CM25</t>
+          <t>3922-1289-CM25</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19839,7 +19839,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>359.22</v>
+        <v>318.16</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3922-1287-CM25</t>
+          <t>3922-1286-CM25</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>164.21</v>
+        <v>307.9</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3922-1289-CM25</t>
+          <t>3922-1287-CM25</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -20008,13 +20008,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>318.16</v>
+        <v>164.21</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>3922-1290-CM25</t>
+          <t>3922-1285-CM25</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20073,13 +20073,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>667.11</v>
+        <v>359.22</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>3922-1288-CM25</t>
+          <t>3922-1284-CM25</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>153.95</v>
+        <v>222.71</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>3922-1295-CM25</t>
+          <t>3922-1299-CM25</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20203,13 +20203,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>305.59</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>3922-1296-CM25</t>
+          <t>3922-1298-CM25</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>50.93</v>
+        <v>305.59</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>3922-1297-CM25</t>
+          <t>3922-1300-CM25</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>101.86</v>
+        <v>509.31</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3922-1298-CM25</t>
+          <t>3922-1296-CM25</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20398,13 +20398,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>305.59</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>3922-1299-CM25</t>
+          <t>3922-1295-CM25</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>101.86</v>
+        <v>305.59</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>3922-1300-CM25</t>
+          <t>3922-1297-CM25</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>509.31</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="310">
@@ -20859,7 +20859,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>4513-170-CM25</t>
+          <t>1075337-15001-CM25</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20879,17 +20879,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20918,13 +20918,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>13587.51</v>
+        <v>5394.24</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1075337-15001-CM25</t>
+          <t>852-430-CM25</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20949,12 +20949,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>5394.24</v>
+        <v>1847.15</v>
       </c>
     </row>
     <row r="317">
@@ -21119,7 +21119,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>852-430-CM25</t>
+          <t>3708-759-CM25</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -21139,17 +21139,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -21178,13 +21178,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>1847.15</v>
+        <v>28614.9</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>3708-759-CM25</t>
+          <t>4513-170-CM25</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -21209,12 +21209,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -21243,7 +21243,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>28614.9</v>
+        <v>13587.51</v>
       </c>
     </row>
     <row r="321">
@@ -21639,7 +21639,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>4337-696-CM25</t>
+          <t>4337-695-CM25</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21698,13 +21698,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>809.55</v>
+        <v>756.27</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>4337-695-CM25</t>
+          <t>4337-696-CM25</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21763,13 +21763,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>756.27</v>
+        <v>809.55</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1075337-15268-CM25</t>
+          <t>3533-400-CM25</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21794,12 +21794,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.101.013-3</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21828,13 +21828,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>25051.58</v>
+        <v>25656.77</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>3533-400-CM25</t>
+          <t>1075337-15268-CM25</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21859,12 +21859,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.101.013-3</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21893,7 +21893,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>25656.77</v>
+        <v>25051.58</v>
       </c>
     </row>
     <row r="331">
@@ -22224,7 +22224,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1950-13966-CM25</t>
+          <t>1968-3215-CM25</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22244,17 +22244,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22283,13 +22283,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>46721.99</v>
+        <v>16313.92</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1968-3215-CM25</t>
+          <t>2202-1081-CM25</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22314,12 +22314,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22348,13 +22348,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>16313.92</v>
+        <v>17564.66</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2202-1081-CM25</t>
+          <t>2103-740-CM25</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22379,12 +22379,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22413,13 +22413,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>17564.66</v>
+        <v>14341.03</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2103-740-CM25</t>
+          <t>1057390-919-CM25</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22478,13 +22478,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>14341.03</v>
+        <v>2911.39</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1057390-919-CM25</t>
+          <t>1950-13966-CM25</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22504,17 +22504,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22543,7 +22543,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2911.39</v>
+        <v>46721.99</v>
       </c>
     </row>
     <row r="341">
@@ -22614,7 +22614,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1057389-10579-CM25</t>
+          <t>1079659-440-CM25</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22639,12 +22639,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22673,13 +22673,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>23894.81</v>
+        <v>1802.9</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1079659-440-CM25</t>
+          <t>1057389-10579-CM25</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22704,12 +22704,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22738,13 +22738,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1802.9</v>
+        <v>23894.81</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1079659-444-CM25</t>
+          <t>3861-276-CM25</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22764,17 +22764,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -22803,13 +22803,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>52274.14</v>
+        <v>6707.59</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3861-276-CM25</t>
+          <t>1079659-444-CM25</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22829,17 +22829,17 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Tolten</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22868,7 +22868,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>6707.59</v>
+        <v>52274.14</v>
       </c>
     </row>
     <row r="346">
@@ -22939,7 +22939,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3836-995-CM25</t>
+          <t>3922-1406-CM25</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22964,12 +22964,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Tolten</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22998,13 +22998,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2666.7</v>
+        <v>41.13</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>3922-1406-CM25</t>
+          <t>3922-1407-CM25</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23063,13 +23063,13 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>41.13</v>
+        <v>61.69</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>3922-1407-CM25</t>
+          <t>3922-1412-CM25</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -23134,7 +23134,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>3922-1412-CM25</t>
+          <t>3836-995-CM25</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -23159,12 +23159,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -23193,7 +23193,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>61.69</v>
+        <v>2666.7</v>
       </c>
     </row>
     <row r="351">
@@ -23589,7 +23589,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1078177-1611-CM25</t>
+          <t>1075337-15489-CM25</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23614,12 +23614,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23648,13 +23648,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>5984.18</v>
+        <v>18694.59</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1075337-15489-CM25</t>
+          <t>1078177-1611-CM25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23679,12 +23679,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>18694.59</v>
+        <v>5984.18</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1078177-1621-CM25</t>
+          <t>1078177-1603-CM25</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>24304.67</v>
+        <v>14128.77</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1057388-1744-CM25</t>
+          <t>1078177-1621-CM25</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23809,12 +23809,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>12049.93</v>
+        <v>24304.67</v>
       </c>
     </row>
     <row r="361">
@@ -23914,7 +23914,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1078177-1603-CM25</t>
+          <t>1057388-1744-CM25</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23939,12 +23939,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23973,7 +23973,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>14128.77</v>
+        <v>12049.93</v>
       </c>
     </row>
     <row r="363">
@@ -25474,7 +25474,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2202-193-CM26</t>
+          <t>1950-417-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25499,12 +25499,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25533,13 +25533,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>552.54</v>
+        <v>23265.02</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1950-417-CM26</t>
+          <t>2202-193-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25564,12 +25564,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25598,7 +25598,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>23265.02</v>
+        <v>552.54</v>
       </c>
     </row>
     <row r="388">
@@ -25734,7 +25734,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1078177-51-CM26</t>
+          <t>1078177-53-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25793,13 +25793,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>3670.18</v>
+        <v>25421.71</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1078177-53-CM26</t>
+          <t>1078177-51-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25858,7 +25858,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>25421.71</v>
+        <v>3670.18</v>
       </c>
     </row>
     <row r="392">
@@ -26124,7 +26124,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2085-172-CM26</t>
+          <t>1383-49-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26144,17 +26144,17 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26183,13 +26183,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1408.02</v>
+        <v>10197.43</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1383-49-CM26</t>
+          <t>2085-172-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26209,17 +26209,17 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26248,7 +26248,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>10197.43</v>
+        <v>1408.02</v>
       </c>
     </row>
     <row r="398">
@@ -26709,7 +26709,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1288819-10-CM26</t>
+          <t>2103-150-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26734,12 +26734,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26768,13 +26768,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>6980.59</v>
+        <v>14607.85</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1057389-1374-CM26</t>
+          <t>1288819-10-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26799,12 +26799,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26833,13 +26833,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>69112.38</v>
+        <v>6980.59</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2103-150-CM26</t>
+          <t>1057389-1374-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26864,12 +26864,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26898,7 +26898,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>14607.85</v>
+        <v>69112.38</v>
       </c>
     </row>
     <row r="408">
@@ -27424,7 +27424,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1079659-102-CM26</t>
+          <t>3533-88-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27449,12 +27449,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.101.013-3</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27483,13 +27483,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>4189.98</v>
+        <v>974.6900000000001</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1383-88-CM26</t>
+          <t>1079659-102-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27509,17 +27509,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27548,13 +27548,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>8418.030000000001</v>
+        <v>4189.98</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>3533-88-CM26</t>
+          <t>1383-88-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27574,17 +27574,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>61.101.013-3</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27613,13 +27613,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>974.6900000000001</v>
+        <v>8418.030000000001</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>707423-44-CM26</t>
+          <t>1057390-209-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27644,12 +27644,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -27678,13 +27678,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>12458.3</v>
+        <v>3510.75</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1057390-209-CM26</t>
+          <t>707423-44-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27709,12 +27709,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27743,13 +27743,13 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>3510.75</v>
+        <v>12458.3</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1075337-7538-CM26</t>
+          <t>3495-66-CM26</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -27774,12 +27774,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -27808,13 +27808,13 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>30267.39</v>
+        <v>16831.8</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2085-244-CM26</t>
+          <t>1075337-7538-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27839,12 +27839,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27873,13 +27873,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>27797.68</v>
+        <v>30267.39</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>3495-66-CM26</t>
+          <t>2085-244-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27904,12 +27904,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27938,7 +27938,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>16831.8</v>
+        <v>27797.68</v>
       </c>
     </row>
     <row r="424">
@@ -28464,7 +28464,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1950-947-CM26</t>
+          <t>1078177-239-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28489,12 +28489,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -28523,13 +28523,13 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>46697.43</v>
+        <v>24693.51</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1078177-249-CM26</t>
+          <t>1950-947-CM26</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -28554,12 +28554,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -28588,13 +28588,13 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>7811.13</v>
+        <v>46697.43</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1078177-239-CM26</t>
+          <t>1078177-249-CM26</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -28653,7 +28653,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>24693.51</v>
+        <v>7811.13</v>
       </c>
     </row>
     <row r="435">
@@ -28789,7 +28789,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1510-113-CM26</t>
+          <t>1057388-173-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -28814,12 +28814,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>60.511.091-6</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE MALLECO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -28848,13 +28848,13 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1387.72</v>
+        <v>14456.26</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>1057388-173-CM26</t>
+          <t>1510-113-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -28879,12 +28879,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>60.511.091-6</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE MALLECO</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -28913,13 +28913,13 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>14456.26</v>
+        <v>1387.72</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>3460-113-CM26</t>
+          <t>655-46-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28939,17 +28939,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>61.101.069-9</t>
+          <t>61.821.000-6</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28978,13 +28978,13 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>1793.36</v>
+        <v>887.71</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>655-46-CM26</t>
+          <t>3460-113-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29004,17 +29004,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>61.821.000-6</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -29043,7 +29043,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>887.71</v>
+        <v>1793.36</v>
       </c>
     </row>
     <row r="441">
@@ -29179,7 +29179,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1075337-7936-CM26</t>
+          <t>2085-361-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -29204,12 +29204,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -29238,13 +29238,13 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>2334.22</v>
+        <v>28360.52</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2085-361-CM26</t>
+          <t>1075337-7908-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -29269,12 +29269,12 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -29303,13 +29303,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>28360.52</v>
+        <v>30593.3</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1075337-7907-CM26</t>
+          <t>1075337-7936-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -29368,13 +29368,13 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>33848.81</v>
+        <v>2334.22</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>1075337-7908-CM26</t>
+          <t>1075337-7907-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -29433,7 +29433,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>30593.3</v>
+        <v>33848.81</v>
       </c>
     </row>
     <row r="447">
@@ -29504,7 +29504,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2202-527-CM26</t>
+          <t>1057389-2366-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29529,12 +29529,12 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>23940.73</v>
+        <v>78178.38</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1057389-2366-CM26</t>
+          <t>2202-527-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -29594,12 +29594,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -29628,7 +29628,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>78178.38</v>
+        <v>23940.73</v>
       </c>
     </row>
     <row r="450">
@@ -30089,7 +30089,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>707423-102-CM26</t>
+          <t>1057388-237-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -30114,12 +30114,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -30148,13 +30148,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>244.01</v>
+        <v>17004.73</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1057388-237-CM26</t>
+          <t>707423-102-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -30179,12 +30179,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -30213,7 +30213,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>17004.73</v>
+        <v>244.01</v>
       </c>
     </row>
     <row r="459">
@@ -30414,7 +30414,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2085-430-CM26</t>
+          <t>2085-426-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -30479,7 +30479,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2085-426-CM26</t>
+          <t>2085-430-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -30739,7 +30739,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>1075337-8408-CM26</t>
+          <t>3151-330-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30759,17 +30759,17 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -30798,13 +30798,13 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>26695.67</v>
+        <v>1281.07</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>3151-330-CM26</t>
+          <t>1075337-8408-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -30824,17 +30824,17 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -30863,7 +30863,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>1281.07</v>
+        <v>26695.67</v>
       </c>
     </row>
     <row r="469">
@@ -30999,7 +30999,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>1075337-8535-CM26</t>
+          <t>1338-64-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -31024,12 +31024,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>60.901.011-8</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -31058,13 +31058,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>42104.53</v>
+        <v>960.75</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1338-64-CM26</t>
+          <t>1075337-8535-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -31089,12 +31089,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>60.901.011-8</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -31123,7 +31123,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>960.75</v>
+        <v>42104.53</v>
       </c>
     </row>
     <row r="473">
@@ -31324,7 +31324,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1078177-493-CM26</t>
+          <t>1078177-491-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -31383,13 +31383,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>18654.71</v>
+        <v>7048.03</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1078177-491-CM26</t>
+          <t>1078177-493-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -31448,13 +31448,13 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>7048.03</v>
+        <v>18654.71</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>1079659-233-CM26</t>
+          <t>1078177-492-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -31479,7 +31479,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -31513,13 +31513,13 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>3118.43</v>
+        <v>31841.32</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>1078177-492-CM26</t>
+          <t>1950-1171-CM26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -31539,17 +31539,17 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -31578,13 +31578,13 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>31841.32</v>
+        <v>43367.05</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1950-1171-CM26</t>
+          <t>1079659-233-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -31604,17 +31604,17 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -31643,7 +31643,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>43367.05</v>
+        <v>3118.43</v>
       </c>
     </row>
     <row r="481">
@@ -33014,7 +33014,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1383-210-CM26</t>
+          <t>1079659-290-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -33034,17 +33034,17 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -33073,13 +33073,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>9748.059999999999</v>
+        <v>56334.37</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1078177-615-CM26</t>
+          <t>1383-210-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -33099,17 +33099,17 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -33138,13 +33138,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>7298.32</v>
+        <v>9748.059999999999</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1079659-290-CM26</t>
+          <t>1078177-615-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -33203,7 +33203,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>56334.37</v>
+        <v>7298.32</v>
       </c>
     </row>
     <row r="505">
@@ -33599,7 +33599,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>3290-214-CM26</t>
+          <t>2085-617-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33624,12 +33624,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -33639,12 +33639,12 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
@@ -33658,13 +33658,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>17910.93</v>
+        <v>31474.4</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2085-617-CM26</t>
+          <t>3290-214-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -33689,12 +33689,12 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -33704,12 +33704,12 @@
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K512" t="inlineStr">
@@ -33723,7 +33723,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>31474.4</v>
+        <v>17910.93</v>
       </c>
     </row>
     <row r="513">
@@ -34314,7 +34314,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1202512-33-CM26</t>
+          <t>1078177-748-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -34339,12 +34339,12 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -34373,13 +34373,13 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>8103.82</v>
+        <v>32787.58</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1078177-745-CM26</t>
+          <t>4337-374-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -34399,17 +34399,17 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -34438,13 +34438,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>7137.91</v>
+        <v>520.1799999999999</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>1078177-746-CM26</t>
+          <t>1202512-33-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34469,12 +34469,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>25653.97</v>
+        <v>8103.82</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1078177-747-CM26</t>
+          <t>1078177-745-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34568,13 +34568,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>19357.46</v>
+        <v>7137.91</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1078177-748-CM26</t>
+          <t>1078177-746-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34633,13 +34633,13 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>32787.58</v>
+        <v>25653.97</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>4337-374-CM26</t>
+          <t>1078177-747-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34659,17 +34659,17 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -34698,7 +34698,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>520.1799999999999</v>
+        <v>19357.46</v>
       </c>
     </row>
     <row r="528">
@@ -35159,7 +35159,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>678-38-CM26</t>
+          <t>1383-263-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -35179,17 +35179,17 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -35218,13 +35218,13 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>2787.65</v>
+        <v>10279.54</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1383-263-CM26</t>
+          <t>678-38-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -35244,17 +35244,17 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -35283,7 +35283,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>10279.54</v>
+        <v>2787.65</v>
       </c>
     </row>
     <row r="537">
@@ -35419,7 +35419,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2085-736-CM26</t>
+          <t>1057390-658-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35439,17 +35439,17 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -35478,13 +35478,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>28639.57</v>
+        <v>10546.93</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>1057390-658-CM26</t>
+          <t>2085-736-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -35504,17 +35504,17 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -35543,7 +35543,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>10546.93</v>
+        <v>28639.57</v>
       </c>
     </row>
     <row r="541">
@@ -35939,7 +35939,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>1075337-9814-CM26</t>
+          <t>1057389-3975-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35964,12 +35964,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35998,13 +35998,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>40322.91</v>
+        <v>74960.91</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1057389-3975-CM26</t>
+          <t>1075337-9814-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -36029,12 +36029,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -36063,7 +36063,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>74960.91</v>
+        <v>40322.91</v>
       </c>
     </row>
     <row r="549">
@@ -36134,7 +36134,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>1079659-377-CM26</t>
+          <t>2103-580-CM26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -36159,12 +36159,12 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -36193,13 +36193,13 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>5233.35</v>
+        <v>17081.23</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2103-580-CM26</t>
+          <t>1079659-377-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36224,12 +36224,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>17081.23</v>
+        <v>5233.35</v>
       </c>
     </row>
     <row r="552">
@@ -36349,7 +36349,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
@@ -36914,7 +36914,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>1057390-712-CM26</t>
+          <t>2057-453-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36934,17 +36934,17 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
@@ -36973,13 +36973,13 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>39837.81</v>
+        <v>163.44</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>2057-453-CM26</t>
+          <t>1057390-712-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36999,17 +36999,17 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -37038,13 +37038,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>163.44</v>
+        <v>39837.81</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2547-221-CM26</t>
+          <t>1075337-9903-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -37064,17 +37064,17 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -37084,17 +37084,17 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L564" t="inlineStr">
@@ -37103,13 +37103,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>1543.11</v>
+        <v>36191.59</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>3434-90-CM26</t>
+          <t>2547-221-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -37129,17 +37129,17 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -37149,17 +37149,17 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L565" t="inlineStr">
@@ -37168,13 +37168,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>35092.36</v>
+        <v>1543.11</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>1075337-9903-CM26</t>
+          <t>3434-90-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -37199,12 +37199,12 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -37233,7 +37233,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>36191.59</v>
+        <v>35092.36</v>
       </c>
     </row>
     <row r="567">
@@ -37299,6 +37299,1631 @@
       </c>
       <c r="M567" s="2" t="n">
         <v>257.81</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>952946-188-CM26</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>65.127.823-6</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M568" s="2" t="n">
+        <v>527.13</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2057-505-CM26</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>70.777.500-9</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M569" s="2" t="n">
+        <v>1443.35</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2085-803-CM26</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>61.602.226-1</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M570" s="2" t="n">
+        <v>30069.31</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2103-635-CM26</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>61.607.402-4</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Hospital  Lonquimay</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M571" s="2" t="n">
+        <v>16223.94</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2066-466-CM26</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>61.602.240-7</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Hospital Galvarino</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M572" s="2" t="n">
+        <v>12151.6</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2085-832-CM26</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>61.602.226-1</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M573" s="2" t="n">
+        <v>2025.23</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2202-1105-CM26</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>61.602.241-5</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M574" s="2" t="n">
+        <v>21771.25</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>1057389-4424-CM26</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>61.602.229-6</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M575" s="2" t="n">
+        <v>72192.52</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>1950-2183-CM26</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>61.602.238-5</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M576" s="2" t="n">
+        <v>50059.06</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>1075337-10257-CM26</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>61.602.222-9</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M577" s="2" t="n">
+        <v>39414.7</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>4406-843-CM26</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>69.180.800-9</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Lumaco</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M578" s="2" t="n">
+        <v>8072.68</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>1075337-10069-CM26</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>61.602.222-9</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M579" s="2" t="n">
+        <v>27354.4</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>1075337-10156-CM26</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>61.602.222-9</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M580" s="2" t="n">
+        <v>6904.99</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2085-842-CM26</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>61.602.226-1</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M581" s="2" t="n">
+        <v>1985.75</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>3290-286-CM26</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>76.032.107-9</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M582" s="2" t="n">
+        <v>9003.98</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>1078177-957-CM26</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M583" s="2" t="n">
+        <v>17481.04</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>1078177-958-CM26</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M584" s="2" t="n">
+        <v>6849.41</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>1078177-961-CM26</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M585" s="2" t="n">
+        <v>30085.44</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>1078177-962-CM26</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M586" s="2" t="n">
+        <v>22930.3</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>1079659-418-CM26</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M587" s="2" t="n">
+        <v>4564.95</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>1523-2425-CM26</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M588" s="2" t="n">
+        <v>610.5</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>4406-873-CM26</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>69.180.800-9</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Lumaco</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M589" s="2" t="n">
+        <v>10096.47</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>1057388-598-CM26</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>61.602.224-5</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M590" s="2" t="n">
+        <v>11769.29</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>4406-887-CM26</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>69.180.800-9</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Lumaco</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M591" s="2" t="n">
+        <v>13095.65</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>1383-320-CM26</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>61.602.242-3</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>HOSPITAL VILCUN</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M592" s="2" t="n">
+        <v>8794.950000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M594"/>
+  <dimension ref="A1:M597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2085-235-CM25</t>
+          <t>1202512-34-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1830.45</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1202512-31-CM25</t>
+          <t>1202512-33-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8689.459999999999</v>
+        <v>755.6</v>
       </c>
     </row>
     <row r="55">
@@ -4024,7 +4024,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1202512-33-CM25</t>
+          <t>2085-235-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>755.6</v>
+        <v>1830.45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1202512-34-CM25</t>
+          <t>1202512-31-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4148,7 +4148,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>21.91</v>
+        <v>8689.459999999999</v>
       </c>
     </row>
     <row r="58">
@@ -4349,7 +4349,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2103-212-CM25</t>
+          <t>4281-49-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>13840.08</v>
+        <v>20917.19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4281-49-CM25</t>
+          <t>2103-212-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>20917.19</v>
+        <v>13840.08</v>
       </c>
     </row>
     <row r="63">
@@ -5259,7 +5259,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3869-312-CM25</t>
+          <t>1383-180-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.191.200-0</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Municipalidad de Gorbea</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>694.71</v>
+        <v>8900.629999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1383-180-CM25</t>
+          <t>3869-312-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>69.191.200-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8900.629999999999</v>
+        <v>694.71</v>
       </c>
     </row>
     <row r="77">
@@ -5454,7 +5454,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2085-374-CM25</t>
+          <t>1079659-166-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>26142.39</v>
+        <v>50284.36</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1079659-166-CM25</t>
+          <t>3533-118-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.101.013-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>50284.36</v>
+        <v>736.1799999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3533-118-CM25</t>
+          <t>2085-374-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.101.013-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>736.1799999999999</v>
+        <v>26142.39</v>
       </c>
     </row>
     <row r="81">
@@ -5714,7 +5714,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1078177-307-CM25</t>
+          <t>1078177-309-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5773,13 +5773,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>34647.94</v>
+        <v>57997.18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1078177-309-CM25</t>
+          <t>4113-281-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>70.766.500-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>57997.18</v>
+        <v>6399.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4113-281-CM25</t>
+          <t>1078177-307-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.766.500-9</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD MELIPEUCO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6399.73</v>
+        <v>34647.94</v>
       </c>
     </row>
     <row r="85">
@@ -5974,7 +5974,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>722-76-CM25</t>
+          <t>3869-351-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.191.200-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>379.28</v>
+        <v>327.77</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3869-351-CM25</t>
+          <t>722-75-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.191.200-0</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Municipalidad de Gorbea</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>327.77</v>
+        <v>618.09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>722-75-CM25</t>
+          <t>722-76-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>618.09</v>
+        <v>379.28</v>
       </c>
     </row>
     <row r="89">
@@ -6234,7 +6234,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057389-3357-CM25</t>
+          <t>2202-427-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>73230.92</v>
+        <v>502.41</v>
       </c>
     </row>
     <row r="91">
@@ -6364,7 +6364,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2202-427-CM25</t>
+          <t>1057389-3357-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6389,12 +6389,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>502.41</v>
+        <v>73230.92</v>
       </c>
     </row>
     <row r="93">
@@ -9159,7 +9159,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>1383-266-CM25</t>
+          <t>2085-554-CM25</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3983.99</v>
+        <v>28593.45</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2085-554-CM25</t>
+          <t>1968-1529-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>28593.45</v>
+        <v>694.23</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1968-1529-CM25</t>
+          <t>1383-266-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9309,17 +9309,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>694.23</v>
+        <v>3983.99</v>
       </c>
     </row>
     <row r="138">
@@ -9679,7 +9679,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>3290-238-CM25</t>
+          <t>3153-210-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>5314.17</v>
+        <v>25970.99</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3153-210-CM25</t>
+          <t>3290-238-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>25970.99</v>
+        <v>5314.17</v>
       </c>
     </row>
     <row r="145">
@@ -9874,7 +9874,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2736-295-CM25</t>
+          <t>1057389-4430-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9894,17 +9894,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9933,13 +9933,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>9075.620000000001</v>
+        <v>31732.94</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1057389-4430-CM25</t>
+          <t>2736-295-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9959,17 +9959,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>31732.94</v>
+        <v>9075.620000000001</v>
       </c>
     </row>
     <row r="148">
@@ -10979,7 +10979,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2202-717-CM25</t>
+          <t>3922-763-CM25</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>15734.66</v>
+        <v>491.71</v>
       </c>
     </row>
     <row r="164">
@@ -11109,7 +11109,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3922-763-CM25</t>
+          <t>2202-717-CM25</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>491.71</v>
+        <v>15734.66</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2103-462-CM25</t>
+          <t>1057389-5099-CM25</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.602.229-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>15469.78</v>
+        <v>35845.23</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1057389-5099-CM25</t>
+          <t>2103-462-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.602.229-6</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11298,7 +11298,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>35845.23</v>
+        <v>15469.78</v>
       </c>
     </row>
     <row r="168">
@@ -11369,7 +11369,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1078177-935-CM25</t>
+          <t>3922-779-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11394,12 +11394,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11428,7 +11428,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1485.54</v>
+        <v>344.33</v>
       </c>
     </row>
     <row r="170">
@@ -11499,7 +11499,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3922-779-CM25</t>
+          <t>1078177-935-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>344.33</v>
+        <v>1485.54</v>
       </c>
     </row>
     <row r="172">
@@ -12474,7 +12474,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1589-94-CM25</t>
+          <t>1079659-310-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12494,17 +12494,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>273.5</v>
+        <v>32477.62</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1589-93-CM25</t>
+          <t>1589-94-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>410.24</v>
+        <v>273.5</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1079659-310-CM25</t>
+          <t>1523-4361-CM25</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12663,13 +12663,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>32477.62</v>
+        <v>1233.23</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1523-4361-CM25</t>
+          <t>1589-93-CM25</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12689,17 +12689,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12728,7 +12728,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1233.23</v>
+        <v>410.24</v>
       </c>
     </row>
     <row r="190">
@@ -13514,7 +13514,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1075337-14064-CM25</t>
+          <t>1075337-14082-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13573,13 +13573,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>13632.62</v>
+        <v>30750.55</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1075337-14082-CM25</t>
+          <t>1057388-1542-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13638,13 +13638,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>30750.55</v>
+        <v>13443.06</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1057388-1542-CM25</t>
+          <t>1075337-14064-CM25</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -13703,7 +13703,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>13443.06</v>
+        <v>13632.62</v>
       </c>
     </row>
     <row r="205">
@@ -13904,7 +13904,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1344300-34-CM25</t>
+          <t>1078177-1131-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13929,12 +13929,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13963,13 +13963,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>190.59</v>
+        <v>24493.61</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1078177-1131-CM25</t>
+          <t>2085-837-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -14028,13 +14028,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>24493.61</v>
+        <v>1997.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2085-837-CM25</t>
+          <t>1078177-1141-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -14093,13 +14093,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>1997.6</v>
+        <v>12941.97</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1078177-1141-CM25</t>
+          <t>1344300-33-CM25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -14124,12 +14124,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14158,13 +14158,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>12941.97</v>
+        <v>1017.73</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1344300-33-CM25</t>
+          <t>1344300-34-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14223,7 +14223,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1017.73</v>
+        <v>190.59</v>
       </c>
     </row>
     <row r="213">
@@ -14359,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3922-942-CM25</t>
+          <t>3922-944-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>496.64</v>
+        <v>397.32</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3922-943-CM25</t>
+          <t>2085-878-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14449,12 +14449,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>198.66</v>
+        <v>30151.24</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3922-944-CM25</t>
+          <t>3922-955-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -14548,13 +14548,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>397.32</v>
+        <v>595.97</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2085-878-CM25</t>
+          <t>3922-956-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14574,17 +14574,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>30151.24</v>
+        <v>546.3099999999999</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>3922-955-CM25</t>
+          <t>3922-942-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>595.97</v>
+        <v>496.64</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3922-956-CM25</t>
+          <t>3922-943-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>546.3099999999999</v>
+        <v>198.66</v>
       </c>
     </row>
     <row r="221">
@@ -17154,7 +17154,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>3922-1144-CM25</t>
+          <t>3922-1145-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -17213,7 +17213,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>202.52</v>
+        <v>101.26</v>
       </c>
     </row>
     <row r="259">
@@ -17284,7 +17284,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>3922-1145-CM25</t>
+          <t>3922-1144-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -17343,7 +17343,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>101.26</v>
+        <v>202.52</v>
       </c>
     </row>
     <row r="261">
@@ -18259,7 +18259,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3922-1225-CM25</t>
+          <t>3922-1226-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18318,7 +18318,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>301.55</v>
+        <v>578.97</v>
       </c>
     </row>
     <row r="276">
@@ -18454,7 +18454,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>3922-1226-CM25</t>
+          <t>3922-1225-CM25</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18513,7 +18513,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>578.97</v>
+        <v>301.55</v>
       </c>
     </row>
     <row r="279">
@@ -22939,7 +22939,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1079659-444-CM25</t>
+          <t>1079659-443-CM25</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22998,13 +22998,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>52274.14</v>
+        <v>30748.5</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1079659-443-CM25</t>
+          <t>1079659-444-CM25</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>30748.5</v>
+        <v>52274.14</v>
       </c>
     </row>
     <row r="349">
@@ -23654,7 +23654,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1075337-15489-CM25</t>
+          <t>1078177-1610-CM25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23679,12 +23679,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23713,13 +23713,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>18694.59</v>
+        <v>19134.27</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1078177-1611-CM25</t>
+          <t>1075337-15489-CM25</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23744,12 +23744,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23778,13 +23778,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>5984.18</v>
+        <v>18694.59</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1078177-1610-CM25</t>
+          <t>1078177-1611-CM25</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>19134.27</v>
+        <v>5984.18</v>
       </c>
     </row>
     <row r="361">
@@ -24694,7 +24694,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1383-2-CM26</t>
+          <t>2202-17-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24714,17 +24714,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24753,13 +24753,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>8698.809999999999</v>
+        <v>15888.24</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2202-17-CM26</t>
+          <t>1383-2-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24779,17 +24779,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24818,7 +24818,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>15888.24</v>
+        <v>8698.809999999999</v>
       </c>
     </row>
     <row r="376">
@@ -25864,7 +25864,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1078177-51-CM26</t>
+          <t>1078177-53-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25923,13 +25923,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>3670.18</v>
+        <v>25421.71</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1078177-53-CM26</t>
+          <t>1078177-51-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25988,13 +25988,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>25421.71</v>
+        <v>3670.18</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>3428-27-CM26</t>
+          <t>1078177-61-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26019,12 +26019,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -26053,13 +26053,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3731.56</v>
+        <v>16895.91</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1078177-61-CM26</t>
+          <t>3428-27-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -26084,12 +26084,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -26118,7 +26118,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>16895.91</v>
+        <v>3731.56</v>
       </c>
     </row>
     <row r="396">
@@ -26254,7 +26254,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1383-49-CM26</t>
+          <t>2085-172-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26274,17 +26274,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,13 +26313,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>10197.43</v>
+        <v>1408.02</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2085-172-CM26</t>
+          <t>1383-49-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26339,17 +26339,17 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26378,7 +26378,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>1408.02</v>
+        <v>10197.43</v>
       </c>
     </row>
     <row r="400">
@@ -26774,7 +26774,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2103-150-CM26</t>
+          <t>1288819-9-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26799,12 +26799,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26833,7 +26833,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>14607.85</v>
+        <v>1745.15</v>
       </c>
     </row>
     <row r="407">
@@ -26969,7 +26969,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1288819-9-CM26</t>
+          <t>2103-150-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26994,12 +26994,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -27028,7 +27028,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1745.15</v>
+        <v>14607.85</v>
       </c>
     </row>
     <row r="410">
@@ -27229,7 +27229,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1078177-161-CM26</t>
+          <t>1078177-158-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27288,13 +27288,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>5553.33</v>
+        <v>21100.98</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1078177-158-CM26</t>
+          <t>1078177-161-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>21100.98</v>
+        <v>5553.33</v>
       </c>
     </row>
     <row r="415">
@@ -27424,7 +27424,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1078177-160-CM26</t>
+          <t>1079659-100-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -27483,13 +27483,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>15984.1</v>
+        <v>50628.25</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1079659-100-CM26</t>
+          <t>1078177-160-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -27548,13 +27548,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>50628.25</v>
+        <v>15984.1</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>3533-88-CM26</t>
+          <t>1383-88-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27574,17 +27574,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>61.101.013-3</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27613,13 +27613,13 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>974.6900000000001</v>
+        <v>8418.030000000001</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1079659-102-CM26</t>
+          <t>3533-88-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27644,12 +27644,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.101.013-3</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -27678,13 +27678,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4189.98</v>
+        <v>974.6900000000001</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1383-88-CM26</t>
+          <t>1079659-102-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27704,17 +27704,17 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27743,7 +27743,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>8418.030000000001</v>
+        <v>4189.98</v>
       </c>
     </row>
     <row r="421">
@@ -27879,7 +27879,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2085-244-CM26</t>
+          <t>1075337-7538-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27904,12 +27904,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27938,13 +27938,13 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>27797.68</v>
+        <v>30267.39</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>3495-66-CM26</t>
+          <t>2085-244-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27969,12 +27969,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -28003,13 +28003,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>16831.8</v>
+        <v>27797.68</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1075337-7538-CM26</t>
+          <t>3495-66-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28034,12 +28034,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>30267.39</v>
+        <v>16831.8</v>
       </c>
     </row>
     <row r="426">
@@ -28204,7 +28204,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2202-406-CM26</t>
+          <t>2103-214-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -28229,12 +28229,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>61.602.241-5</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -28263,13 +28263,13 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>259.96</v>
+        <v>16908.37</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2103-214-CM26</t>
+          <t>2202-406-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28294,12 +28294,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>61.602.241-5</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL CURACAUTIN</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>16908.37</v>
+        <v>259.96</v>
       </c>
     </row>
     <row r="430">
@@ -28724,7 +28724,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1078177-240-CM26</t>
+          <t>1078177-239-CM26</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -28783,13 +28783,13 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>32651.46</v>
+        <v>24693.51</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1078177-239-CM26</t>
+          <t>1078177-240-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -28848,7 +28848,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>24693.51</v>
+        <v>32651.46</v>
       </c>
     </row>
     <row r="438">
@@ -28919,7 +28919,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1510-113-CM26</t>
+          <t>1057388-173-CM26</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -28944,12 +28944,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>60.511.091-6</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE MALLECO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -28978,13 +28978,13 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>1387.72</v>
+        <v>14456.26</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1057388-173-CM26</t>
+          <t>1510-113-CM26</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -29009,12 +29009,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>60.511.091-6</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE MALLECO</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -29043,7 +29043,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>14456.26</v>
+        <v>1387.72</v>
       </c>
     </row>
     <row r="441">
@@ -29179,7 +29179,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1383-130-CM26</t>
+          <t>1079659-150-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -29199,17 +29199,17 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -29238,13 +29238,13 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>9542.709999999999</v>
+        <v>54512.01</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1079659-150-CM26</t>
+          <t>1383-130-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -29264,17 +29264,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -29303,7 +29303,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>54512.01</v>
+        <v>9542.709999999999</v>
       </c>
     </row>
     <row r="445">
@@ -29374,7 +29374,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>1075337-7908-CM26</t>
+          <t>1075337-7907-CM26</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -29433,13 +29433,13 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>30593.3</v>
+        <v>33848.81</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1075337-7936-CM26</t>
+          <t>1075337-7908-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -29498,13 +29498,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2334.22</v>
+        <v>30593.3</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>1075337-7907-CM26</t>
+          <t>1075337-7936-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29563,7 +29563,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>33848.81</v>
+        <v>2334.22</v>
       </c>
     </row>
     <row r="449">
@@ -29764,7 +29764,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1075337-8158-CM26</t>
+          <t>1075337-8157-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>35624.39</v>
+        <v>3416.58</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1075337-8157-CM26</t>
+          <t>1075337-8158-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29888,7 +29888,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>3416.58</v>
+        <v>35624.39</v>
       </c>
     </row>
     <row r="454">
@@ -30349,7 +30349,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1079659-191-CM26</t>
+          <t>809-42-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -30374,12 +30374,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -30408,13 +30408,13 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>56095.67</v>
+        <v>2738.2</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>809-42-CM26</t>
+          <t>1079659-191-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -30439,12 +30439,12 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -30473,7 +30473,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>2738.2</v>
+        <v>56095.67</v>
       </c>
     </row>
     <row r="463">
@@ -30544,7 +30544,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>1078177-407-CM26</t>
+          <t>2085-430-CM26</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -30569,12 +30569,12 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>295.08</v>
+        <v>2229.87</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2085-430-CM26</t>
+          <t>2085-426-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30674,7 +30674,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>2085-426-CM26</t>
+          <t>2085-424-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30733,13 +30733,13 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>2229.87</v>
+        <v>31942.39</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2085-424-CM26</t>
+          <t>1078177-407-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30764,12 +30764,12 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -30798,7 +30798,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>31942.39</v>
+        <v>295.08</v>
       </c>
     </row>
     <row r="468">
@@ -31129,7 +31129,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1338-64-CM26</t>
+          <t>1075337-8535-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -31154,12 +31154,12 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>60.901.011-8</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
@@ -31188,13 +31188,13 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>960.75</v>
+        <v>42104.53</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1075337-8535-CM26</t>
+          <t>1338-64-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -31219,12 +31219,12 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>60.901.011-8</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -31253,7 +31253,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>42104.53</v>
+        <v>960.75</v>
       </c>
     </row>
     <row r="475">
@@ -31584,7 +31584,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1078177-492-CM26</t>
+          <t>1950-1171-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -31604,17 +31604,17 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -31643,7 +31643,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>31841.32</v>
+        <v>43367.05</v>
       </c>
     </row>
     <row r="481">
@@ -31714,7 +31714,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1950-1171-CM26</t>
+          <t>1078177-492-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31734,17 +31734,17 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>43367.05</v>
+        <v>31841.32</v>
       </c>
     </row>
     <row r="483">
@@ -31844,7 +31844,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>722-67-CM26</t>
+          <t>722-68-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31903,13 +31903,13 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>431.8</v>
+        <v>416.91</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>722-68-CM26</t>
+          <t>722-67-CM26</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -31968,7 +31968,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>416.91</v>
+        <v>431.8</v>
       </c>
     </row>
     <row r="486">
@@ -32364,7 +32364,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>1075337-8783-CM26</t>
+          <t>1075337-8782-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32423,13 +32423,13 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>6449.92</v>
+        <v>24574.66</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1075337-8782-CM26</t>
+          <t>1075337-8783-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -32488,7 +32488,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>24574.66</v>
+        <v>6449.92</v>
       </c>
     </row>
     <row r="494">
@@ -33729,7 +33729,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2085-617-CM26</t>
+          <t>3290-214-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33754,12 +33754,12 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
@@ -33769,12 +33769,12 @@
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K513" t="inlineStr">
@@ -33788,13 +33788,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>31474.4</v>
+        <v>17910.93</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>3290-214-CM26</t>
+          <t>2085-617-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33819,12 +33819,12 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K514" t="inlineStr">
@@ -33853,7 +33853,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>17910.93</v>
+        <v>31474.4</v>
       </c>
     </row>
     <row r="515">
@@ -34574,7 +34574,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1202512-33-CM26</t>
+          <t>1078177-746-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34599,12 +34599,12 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
@@ -34633,13 +34633,13 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>8103.82</v>
+        <v>25653.97</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1078177-746-CM26</t>
+          <t>4337-374-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34659,17 +34659,17 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -34698,13 +34698,13 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>25653.97</v>
+        <v>520.1799999999999</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1078177-745-CM26</t>
+          <t>1202512-33-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34729,12 +34729,12 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -34763,13 +34763,13 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>7137.91</v>
+        <v>8103.82</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>4337-374-CM26</t>
+          <t>1078177-745-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34789,17 +34789,17 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -34828,7 +34828,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>520.1799999999999</v>
+        <v>7137.91</v>
       </c>
     </row>
     <row r="530">
@@ -35094,7 +35094,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>707423-186-CM26</t>
+          <t>2057-378-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -35114,17 +35114,17 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -35153,13 +35153,13 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>185.15</v>
+        <v>1031.05</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2057-378-CM26</t>
+          <t>707423-186-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -35179,17 +35179,17 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -35218,7 +35218,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>1031.05</v>
+        <v>185.15</v>
       </c>
     </row>
     <row r="536">
@@ -35419,7 +35419,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>1426099-177-CM26</t>
+          <t>2066-419-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35439,17 +35439,17 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.602.240-7</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Hospital Galvarino</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -35478,13 +35478,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2647.93</v>
+        <v>12710.29</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2066-419-CM26</t>
+          <t>1426099-177-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -35504,17 +35504,17 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>61.602.240-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Hospital Galvarino</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -35543,13 +35543,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>12710.29</v>
+        <v>2647.93</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1057390-658-CM26</t>
+          <t>2085-736-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35574,12 +35574,12 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
@@ -35608,13 +35608,13 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>10546.93</v>
+        <v>28639.57</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2085-736-CM26</t>
+          <t>1057390-658-CM26</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -35639,12 +35639,12 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -35673,7 +35673,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>28639.57</v>
+        <v>10546.93</v>
       </c>
     </row>
     <row r="543">
@@ -35744,7 +35744,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1075337-9506-CM26</t>
+          <t>2057-405-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -35764,17 +35764,17 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -35803,13 +35803,13 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>37962.21</v>
+        <v>2357.79</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2057-405-CM26</t>
+          <t>1075337-9506-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35829,17 +35829,17 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -35868,7 +35868,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>2357.79</v>
+        <v>37962.21</v>
       </c>
     </row>
     <row r="546">
@@ -36394,7 +36394,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>1950-1858-CM26</t>
+          <t>1075337-9863-CM26</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -36419,12 +36419,12 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>61.602.238-5</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -36453,13 +36453,13 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>51888.77</v>
+        <v>6791.22</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>1075337-9863-CM26</t>
+          <t>1950-1858-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -36484,12 +36484,12 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.602.238-5</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO SALUD ARAUCANIA SUR HOSPITAL PITRUFQUEN</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -36518,13 +36518,13 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>6791.22</v>
+        <v>51888.77</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1202512-34-CM26</t>
+          <t>1057388-538-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -36549,12 +36549,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>60.511.090-8</t>
+          <t>61.602.224-5</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -36583,13 +36583,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>731.05</v>
+        <v>15625.47</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>1057388-538-CM26</t>
+          <t>1202512-34-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -36614,12 +36614,12 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>61.602.224-5</t>
+          <t>60.511.090-8</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL PUREN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -36648,7 +36648,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>15625.47</v>
+        <v>731.05</v>
       </c>
     </row>
     <row r="558">
@@ -37044,7 +37044,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2057-453-CM26</t>
+          <t>1057390-712-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -37064,17 +37064,17 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>70.777.500-9</t>
+          <t>61.955.100-1</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD ARTURO PRAT</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -37103,13 +37103,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>163.44</v>
+        <v>39837.81</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>1057390-712-CM26</t>
+          <t>2057-453-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -37129,17 +37129,17 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>61.955.100-1</t>
+          <t>70.777.500-9</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+          <t>UNIVERSIDAD ARTURO PRAT</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -37168,13 +37168,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>39837.81</v>
+        <v>163.44</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2547-221-CM26</t>
+          <t>3434-90-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -37194,17 +37194,17 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H566" t="inlineStr">
@@ -37214,17 +37214,17 @@
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>76.045.081-2</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
@@ -37233,13 +37233,13 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>1543.11</v>
+        <v>35092.36</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>3434-90-CM26</t>
+          <t>1075337-9903-CM26</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -37264,12 +37264,12 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -37298,13 +37298,13 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>35092.36</v>
+        <v>36191.59</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>1075337-9903-CM26</t>
+          <t>2547-221-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -37324,17 +37324,17 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -37344,17 +37344,17 @@
       </c>
       <c r="I568" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SOCIEDAD DE CONFECCIONES CLER LIMITADA</t>
         </is>
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.045.081-2</t>
         </is>
       </c>
       <c r="K568" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L568" t="inlineStr">
@@ -37363,7 +37363,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>36191.59</v>
+        <v>1543.11</v>
       </c>
     </row>
     <row r="569">
@@ -38019,7 +38019,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1075337-10257-CM26</t>
+          <t>1075337-10069-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -38078,13 +38078,13 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>39414.7</v>
+        <v>27354.4</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>4406-843-CM26</t>
+          <t>1075337-10156-CM26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -38104,17 +38104,17 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -38143,13 +38143,13 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>8072.68</v>
+        <v>6904.99</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>1075337-10069-CM26</t>
+          <t>1075337-10257-CM26</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>27354.4</v>
+        <v>39414.7</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>1075337-10156-CM26</t>
+          <t>4406-843-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -38234,17 +38234,17 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -38273,13 +38273,13 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>6904.99</v>
+        <v>8072.68</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>2085-842-CM26</t>
+          <t>3290-286-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -38299,17 +38299,17 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -38319,12 +38319,12 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K583" t="inlineStr">
@@ -38338,13 +38338,13 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>1985.75</v>
+        <v>9003.98</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>3290-286-CM26</t>
+          <t>2085-842-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -38364,17 +38364,17 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -38384,12 +38384,12 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
@@ -38403,7 +38403,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>9003.98</v>
+        <v>1985.75</v>
       </c>
     </row>
     <row r="585">
@@ -38929,7 +38929,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>4406-887-CM26</t>
+          <t>1383-320-CM26</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -38954,12 +38954,12 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>61.602.242-3</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>HOSPITAL VILCUN</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
@@ -38988,13 +38988,13 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>13095.65</v>
+        <v>8794.950000000001</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>1383-320-CM26</t>
+          <t>4406-887-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -39019,12 +39019,12 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>61.602.242-3</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>HOSPITAL VILCUN</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -39053,7 +39053,202 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>8794.950000000001</v>
+        <v>13095.65</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>1079659-425-CM26</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M595" s="2" t="n">
+        <v>52104.24</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>1057390-825-CM26</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>61.955.100-1</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M596" s="2" t="n">
+        <v>38592.42</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>1202512-44-CM26</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>60.511.090-8</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M597" s="2" t="n">
+        <v>403.9</v>
       </c>
     </row>
   </sheetData>
